--- a/data/raw/sales/Week 19/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 19/Audio_Array/other_channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 19\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F74447-A639-4AD8-AB71-67D3F54FA769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E471C10-8538-48A3-BCB8-612D9040902C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="405">
   <si>
     <t>SKU</t>
   </si>
@@ -1264,7 +1264,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1295,27 +1295,26 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1344,7 +1343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1406,30 +1405,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -1447,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1521,25 +1496,13 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2358,7 +2321,7 @@
       <c r="B6" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="29" t="s">
         <v>130</v>
       </c>
       <c r="D6" s="24">
@@ -2378,7 +2341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:U916"/>
+  <dimension ref="A1:U909"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2426,146 +2389,165 @@
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>22871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>16011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>11925</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="F2" s="30">
-        <v>8642.3700000000008</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="29">
-        <v>21</v>
-      </c>
-      <c r="F3" s="30">
-        <v>33795.760000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="29">
-        <v>5</v>
-      </c>
-      <c r="F4" s="30">
-        <v>11266.95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="29">
-        <v>1</v>
-      </c>
-      <c r="F5" s="30">
-        <v>4066.95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="29">
-        <v>4</v>
-      </c>
-      <c r="F6" s="30">
-        <v>11925.42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>348</v>
-      </c>
-      <c r="E7" s="29">
-        <v>3</v>
-      </c>
-      <c r="F7" s="30">
-        <v>4022.88</v>
+      <c r="F7">
+        <v>3219</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
     <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3466,13 +3448,6 @@
     <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -5856,7 +5831,7 @@
       <c r="A2" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="27" t="s">
         <v>163</v>
       </c>
       <c r="C2" s="17" t="s">
@@ -5868,10 +5843,10 @@
       <c r="E2" s="17">
         <v>2881</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="31" t="s">
+      <c r="F2" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="27" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5879,7 +5854,7 @@
       <c r="A3" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="17" t="s">
@@ -5891,10 +5866,10 @@
       <c r="E3" s="13">
         <v>53200</v>
       </c>
-      <c r="F3" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="31" t="s">
+      <c r="F3" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>401</v>
       </c>
     </row>
@@ -5902,7 +5877,7 @@
       <c r="A4" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="27" t="s">
         <v>207</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -5914,10 +5889,10 @@
       <c r="E4" s="13">
         <v>56000</v>
       </c>
-      <c r="F4" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="F4" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>401</v>
       </c>
     </row>
@@ -5925,7 +5900,7 @@
       <c r="A5" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="27" t="s">
         <v>404</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -5937,10 +5912,10 @@
       <c r="E5" s="13">
         <v>44100</v>
       </c>
-      <c r="F5" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="31" t="s">
+      <c r="F5" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>401</v>
       </c>
     </row>
